--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -488,10 +488,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_受入条件表.xlsx で行います。</t>
-        </is>
-      </c>
-    </row>
+          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_確認表.xlsx で行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -558,7 +559,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>受入条件表 20260805_01</t>
+          <t>確認表 20260805_01</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -616,6 +617,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -685,6 +687,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -806,6 +809,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -950,6 +954,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -1019,6 +1024,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -1073,6 +1079,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -1144,8 +1151,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -488,11 +488,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_確認表.xlsx で行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_受入条件表.xlsx で行います。</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -559,7 +558,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>確認表 20260805_01</t>
+          <t>受入条件表 20260805_01</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -617,7 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -687,7 +685,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -809,7 +806,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
@@ -954,7 +950,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -1024,7 +1019,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -1079,7 +1073,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
@@ -1151,8 +1144,8 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>仕様書 20260803_01</t>
+          <t>仕様書 20260803_01_..._PdM版.md</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>受入条件表 20260805_01</t>
+          <t>受入条件表 20260805_01_確認表.xlsx</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>検証プラン 20260805_02</t>
+          <t>検証プラン 20260805_02_検証プラン.xlsx</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>検証データセット data/01〜18</t>
+          <t>検証データセット data/01〜19（19ファイル）</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1076,7 +1076,7 @@
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ 7. 判断の状態（2026-08-05 時点）</t>
+          <t>■ 7. 判断の状態（2026-08-07 時点）</t>
         </is>
       </c>
     </row>
@@ -1097,25 +1097,25 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1">
+    <row r="52" ht="56" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（いずれも2026-08-03 確定）</t>
+          <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（2026-08-03 確定）　判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる ／ 判断10 設定編集の入口はA（両方残す・更新処理を1箇所に集約）（2026-08-07 第1回ジャッジで確定）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>暫定適用（要確認）</t>
+          <t>未確定</t>
         </is>
       </c>
       <c r="B53" s="8" t="n">
@@ -1123,22 +1123,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>判断2 翌月差額調整の費目 ／ 判断3・4 画面名の統一 ／ 判断10 設定編集の入口を2つ残すか（実装前に確定が必要）</t>
+          <t>判断2 翌月差額調整の費目 ／ 判断3・4 画面名の統一（いずれもリリースまでに確定させる）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,14 +95,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_受入条件表.xlsx で行います。</t>
+          <t>言葉の定義だけを載せています。実際の判定は 20260805_従業員管理_01_確認表.xlsx で行います。</t>
         </is>
       </c>
     </row>
@@ -499,20 +493,20 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2と3は独立して使えます。受入条件表は合格ラインと確認する画面だけで判定でき、検証プランは操作と期待値だけで実施できます。相互参照は「対応検証ID」「対応ID」で行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
+          <t>2と3は独立して使えます。受入条件表は合格ラインと確認する画面だけで判定でき、検証プランは操作と期待値だけで実施できます。相互参照は「対応検証ID」「対応受入条件」で行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>層</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>文書</t>
         </is>
@@ -528,89 +522,89 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>1. 意図</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>仕様書 20260803_01_..._PdM版.md</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>なぜそう作るか。11フローのケース別遷移。判断の記録（確定3・未確定4・暫定3）</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>なぜそう作るか。11フローのケース別遷移。判断の記録</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>PdM</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="79" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2. 合格ライン</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>受入条件表 20260805_01_確認表.xlsx</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>意図を満たしたと言える定量条件。実装レベルとマイルストーン</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>PdM＋エンジニア</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="9" ht="79" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>3. 挙動</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>検証プラン 20260805_02_検証プラン.xlsx</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>その条件を実際の画面・データでどう確かめるか</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>検証実施者</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="94" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>4. 前提データ</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>検証データセット data/01〜19（19ファイル）</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>検証に必要な入力データ。算式で再現できる値</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>検証実施者</t>
         </is>
@@ -623,13 +617,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="19" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>実装レベル</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
@@ -640,46 +634,46 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>L0 リリース不可</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>1件でも落ちるとリリースしない。過去が動く／締めても動く／店舗別が全社と合わない、のいずれかが起きている状態</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>L1 MVP必須</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>業務が回る最低ライン。「実装できていないと起きること」が【不可】なら落とせない、【条件付きGo可】なら手作業で代替できる</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>L2 次段階</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>今回は実装しない。実測を記録し次の優先順位を決める</t>
         </is>
@@ -692,20 +686,20 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>リソースが足りない場合の確保順は M1 → M5 → M2 → M3 → M4。M1を飛ばして画面から作ると、その期間のデータは適用日付と履歴を持たず、あとから正しい過去を作れません。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="19" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>マイルストーン</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>条件数</t>
         </is>
@@ -716,91 +710,91 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>M1 過去が動かない構造ができる</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>設定が適用日付つきで保存され、履歴が積まれる。同じ従業員コードが二重に登録されない　※適用日付と履歴は後から遡って作れないため最優先</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>設定が適用日付つきで保存され、履歴が積まれる。同じ従業員コードが二重に登録されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>M2 金額が算式どおりに出る</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
+      <c r="B22" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>確定した算式で人件費が計算され、店舗別の合計が全社と一致する</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>M3 月次を確定して外部へ渡せる</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
+      <c r="B23" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>締めた月は動かず、解除すれば再計算される。締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>M4 顧客とCSが自分で運用できる</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>CSVで取り込め、必要な項目だけ出力でき、数字がおかしいときに原因を追える</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>M5 既存顧客を壊さない</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>移行しても既存データと過去月の人件費が変わらない</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>M6 次段階（今回は実装しない）</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
+      <c r="B26" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>無くても業務は回る。実測を記録し次の優先順位を決める</t>
         </is>
@@ -813,13 +807,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="19" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>設計ポイント</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>条件数</t>
         </is>
@@ -830,123 +824,123 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>移行</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B30" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>AC-02 ／ AC-01 ／ AC-03</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>原則①</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
+      <c r="B31" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>AC-04 ／ AC-06 ／ AC-07 ／ AC-08 ／ AC-09 ／ AC-05 ／ AC-49</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>データ保全</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>AC-40 ／ AC-23 ／ AC-34 ／ AC-42 ／ AC-43 ／ AC-44 ／ AC-50</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>原則③</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>AC-47 ／ AC-11 ／ AC-14 ／ AC-15</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>原則②</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>AC-16 ／ AC-17 ／ AC-18 ／ AC-19 ／ AC-20 ／ AC-41 ／ AC-32 ／ AC-45</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>入出力</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>AC-21 ／ AC-22 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-27 ／ AC-28 ／ AC-36 ／ AC-37 ／ AC-39 ／ AC-38 ／ AC-48 ／ AC-51</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="B37" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46</t>
+      <c r="B37" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53</t>
         </is>
       </c>
     </row>
@@ -957,13 +951,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
+    <row r="40" ht="19" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>価値</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>条件数</t>
         </is>
@@ -974,46 +968,46 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>V1 数字が動かない</t>
         </is>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>過去の月も確定した月もあとから金額が変わらない。欠けると数字が信用されずExcelに戻る</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>V3 自分で運用できる</t>
         </is>
       </c>
-      <c r="B42" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="B42" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>導入・説明・外部提出を開発に依頼せず回せる。欠けると運用が開発待ちになる</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>V2 数字が実態を表す</t>
         </is>
       </c>
-      <c r="B43" s="8" t="n">
+      <c r="B43" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>金額が算式どおりで、店舗別が実際の働き方と一致する。欠けると店舗別PLが使えない</t>
         </is>
@@ -1026,13 +1020,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="19" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
@@ -1043,50 +1037,50 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="B47" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="B47" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>画面を操作すれば判定できる</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="B48" s="8" t="n">
+      <c r="B48" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>画面を操作しても実装の是非を判別できない。実装物（スキーマ・API・コード）を提示してもらって確認する（検証プラン R-01〜R-06）。例：画面側だけで必須チェックしていても操作では合格に見えるが、APIを直接呼べば不正な登録ができる</t>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>画面を操作しても実装の是非を判別できない。実装物（スキーマ・API・コード）を提示してもらって確認する（検証プラン R-01〜R-06）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ 7. 判断の状態（2026-08-07 時点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="18" customHeight="1">
+          <t>■ 7. 判断の状態（2026-08-13 時点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
@@ -1097,31 +1091,31 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="56" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="B52" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（2026-08-03 確定）　判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる ／ 判断10 設定編集の入口はA（両方残す・更新処理を1箇所に集約）（2026-08-07 第1回ジャッジで確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+      <c r="B52" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（2026-08-03）　判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる ／ 判断10 設定編集の入口はA（両方残す・更新処理を1箇所に集約）（2026-08-07）　判断11 設定変更履歴は直近3件・降順・ステータス2列目・変更点を強調（2026-08-13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="B53" s="8" t="n">
+      <c r="B53" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>判断2 翌月差額調整の費目 ／ 判断3・4 画面名の統一（いずれもリリースまでに確定させる）</t>
         </is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53</t>
+          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53 ／ AC-54</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>検証データセット data/01〜19（19ファイル）</t>
+          <t>検証データセット data/01〜20（20ファイル）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -861,11 +861,11 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>AC-40 ／ AC-23 ／ AC-34 ／ AC-42 ／ AC-43 ／ AC-44 ／ AC-50</t>
+          <t>AC-40 ／ AC-23 ／ AC-34 ／ AC-42 ／ AC-43 ／ AC-44 ／ AC-50 ／ AC-55</t>
         </is>
       </c>
     </row>
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>AC-21 ／ AC-22 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-27 ／ AC-28 ／ AC-36 ／ AC-37 ／ AC-39 ／ AC-38 ／ AC-48 ／ AC-51</t>
+          <t>AC-21 ／ AC-22 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-27 ／ AC-28 ／ AC-36 ／ AC-37 ／ AC-39 ／ AC-38 ／ AC-48 ／ AC-51 ／ AC-56</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53 ／ AC-54</t>
+          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53 ／ AC-54 ／ AC-57</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53 ／ AC-54 ／ AC-57</t>
+          <t>AC-29 ／ AC-30 ／ AC-33 ／ AC-31 ／ AC-46 ／ AC-52 ／ AC-53 ／ AC-54 ／ AC-57 ／ AC-58</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -891,11 +891,11 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35</t>
+          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -891,11 +891,11 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59</t>
+          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59 ／ AC-60</t>
         </is>
       </c>
     </row>
@@ -1013,109 +1013,120 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>V1 数字が見える</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>■ 6. 確認方法の定義</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>画面を操作すれば判定できる</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>画面を操作しても実装の是非を判別できない。実装物（スキーマ・API・コード）を提示してもらって確認する（検証プラン R-01〜R-06）</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>■ 7. 判断の状態（2026-08-13 時点）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="52" ht="19" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="64" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B53" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（2026-08-03）　判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる ／ 判断10 設定編集の入口はA（両方残す・更新処理を1箇所に集約）（2026-08-07）　判断11 設定変更履歴は直近3件・降順・ステータス2列目・変更点を強調（2026-08-13）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B54" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>判断2 翌月差額調整の費目 ／ 判断3・4 画面名の統一（いずれもリリースまでに確定させる）</t>
         </is>
@@ -1124,14 +1135,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A46:D46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -906,11 +906,11 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>AC-16 ／ AC-17 ／ AC-18 ／ AC-19 ／ AC-20 ／ AC-41 ／ AC-32 ／ AC-45</t>
+          <t>AC-16 ／ AC-17 ／ AC-18 ／ AC-19 ／ AC-20 ／ AC-41 ／ AC-32 ／ AC-45 ／ AC-61</t>
         </is>
       </c>
     </row>
@@ -1024,109 +1024,120 @@
       </c>
       <c r="C44" s="6" t="inlineStr"/>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>V3 過去が動かない</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>■ 6. 確認方法の定義</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>画面を操作すれば判定できる</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>画面を操作しても実装の是非を判別できない。実装物（スキーマ・API・コード）を提示してもらって確認する（検証プラン R-01〜R-06）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>■ 7. 判断の状態（2026-08-13 時点）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B54" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>判断1 所定労働日割 ／ 判断5 ヘルプ人件費は振替 ／ 判断6 交通費は独立費目（2026-08-03）　判断7 深夜割増1.5 ／ 判断8 みなし超過1.25・未達は減額なし ／ 判断9 端数は所属店舗に寄せる ／ 判断10 設定編集の入口はA（両方残す・更新処理を1箇所に集約）（2026-08-07）　判断11 設定変更履歴は直近3件・降順・ステータス2列目・変更点を強調（2026-08-13）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="19" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B55" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>判断2 翌月差額調整の費目 ／ 判断3・4 画面名の統一（いずれもリリースまでに確定させる）</t>
         </is>
@@ -1139,10 +1150,10 @@
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A46:D46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -891,11 +891,11 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59 ／ AC-60</t>
+          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59 ／ AC-60 ／ AC-62</t>
         </is>
       </c>
     </row>
@@ -906,11 +906,11 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>AC-16 ／ AC-17 ／ AC-18 ／ AC-19 ／ AC-20 ／ AC-41 ／ AC-32 ／ AC-45 ／ AC-61</t>
+          <t>AC-16 ／ AC-17 ／ AC-18 ／ AC-19 ／ AC-20 ／ AC-41 ／ AC-32 ／ AC-45 ／ AC-61 ／ AC-63</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" s="6" t="inlineStr"/>
     </row>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -846,11 +846,11 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>AC-04 ／ AC-06 ／ AC-07 ／ AC-08 ／ AC-09 ／ AC-05 ／ AC-49</t>
+          <t>AC-04 ／ AC-06 ／ AC-07 ／ AC-08 ／ AC-09 ／ AC-05 ／ AC-49 ／ AC-66</t>
         </is>
       </c>
     </row>
@@ -891,11 +891,11 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59 ／ AC-60 ／ AC-62</t>
+          <t>AC-10 ／ AC-12 ／ AC-13 ／ AC-35 ／ AC-59 ／ AC-60 ／ AC-62 ／ AC-64 ／ AC-65 ／ AC-67</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="inlineStr"/>
     </row>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>

--- a/20260805_従業員管理_00_定義表.xlsx
+++ b/20260805_従業員管理_00_定義表.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>AC-21 ／ AC-22 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-27 ／ AC-28 ／ AC-36 ／ AC-37 ／ AC-39 ／ AC-38 ／ AC-48 ／ AC-51 ／ AC-56</t>
+          <t>AC-21 ／ AC-22 ／ AC-24 ／ AC-25 ／ AC-26 ／ AC-27 ／ AC-28 ／ AC-36 ／ AC-37 ／ AC-39 ／ AC-38 ／ AC-48 ／ AC-51 ／ AC-56 ／ AC-68</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
